--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/152.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/152.xlsx
@@ -426,13 +426,13 @@
         <v>-5.5450413256494</v>
       </c>
       <c r="E2">
-        <v>-8.472939970123116</v>
+        <v>-9.732557657726666</v>
       </c>
       <c r="F2">
-        <v>-4.67158547212726</v>
+        <v>-4.977905870291559</v>
       </c>
       <c r="G2">
-        <v>-4.928757902262974</v>
+        <v>-5.93077727336188</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-5.054336549588</v>
       </c>
       <c r="E3">
-        <v>-9.464988242509454</v>
+        <v>-10.23923050054887</v>
       </c>
       <c r="F3">
-        <v>-4.683706365351076</v>
+        <v>-5.097005306250351</v>
       </c>
       <c r="G3">
-        <v>-4.290319195014525</v>
+        <v>-5.068072279646584</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-4.552911908296723</v>
       </c>
       <c r="E4">
-        <v>-9.32955064188805</v>
+        <v>-10.3549601822889</v>
       </c>
       <c r="F4">
-        <v>-4.586871459004489</v>
+        <v>-5.015812663230559</v>
       </c>
       <c r="G4">
-        <v>-4.861990819826953</v>
+        <v>-5.1717453237544</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.085274080331619</v>
       </c>
       <c r="E5">
-        <v>-10.50858866299911</v>
+        <v>-10.93698683259873</v>
       </c>
       <c r="F5">
-        <v>-4.753012503622537</v>
+        <v>-4.877860000201418</v>
       </c>
       <c r="G5">
-        <v>-4.507881626764349</v>
+        <v>-5.544413435110157</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.623956434643342</v>
       </c>
       <c r="E6">
-        <v>-11.11922168361541</v>
+        <v>-11.43180865894287</v>
       </c>
       <c r="F6">
-        <v>-4.449728861551095</v>
+        <v>-4.943309022715826</v>
       </c>
       <c r="G6">
-        <v>-3.383352207439173</v>
+        <v>-5.025137814547776</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.1568306162558</v>
       </c>
       <c r="E7">
-        <v>-11.78912337204409</v>
+        <v>-11.62279705021636</v>
       </c>
       <c r="F7">
-        <v>-4.474888405576723</v>
+        <v>-4.782458347708303</v>
       </c>
       <c r="G7">
-        <v>-4.212067830102772</v>
+        <v>-4.724427721033616</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-2.668822801658884</v>
       </c>
       <c r="E8">
-        <v>-12.17804230524484</v>
+        <v>-12.16252322482056</v>
       </c>
       <c r="F8">
-        <v>-4.422778146135103</v>
+        <v>-5.186697698918306</v>
       </c>
       <c r="G8">
-        <v>-3.826227058046254</v>
+        <v>-4.925215618535954</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-2.151732824123175</v>
       </c>
       <c r="E9">
-        <v>-12.2222356830857</v>
+        <v>-14.25433858081369</v>
       </c>
       <c r="F9">
-        <v>-4.473879584908588</v>
+        <v>-4.91753737635388</v>
       </c>
       <c r="G9">
-        <v>-2.63087513799945</v>
+        <v>-4.468456339937169</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-1.609283638929397</v>
       </c>
       <c r="E10">
-        <v>-14.17825116053681</v>
+        <v>-13.80987791390886</v>
       </c>
       <c r="F10">
-        <v>-4.271169186997128</v>
+        <v>-5.19381170589046</v>
       </c>
       <c r="G10">
-        <v>-2.80562228428988</v>
+        <v>-4.228272950517504</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-1.050705202163102</v>
       </c>
       <c r="E11">
-        <v>-14.72411341742139</v>
+        <v>-14.60791730285858</v>
       </c>
       <c r="F11">
-        <v>-4.368583729708766</v>
+        <v>-5.138770006799362</v>
       </c>
       <c r="G11">
-        <v>-2.084774166932354</v>
+        <v>-3.872160877403642</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-0.5005232758970054</v>
       </c>
       <c r="E12">
-        <v>-14.79032423588754</v>
+        <v>-15.5821867862908</v>
       </c>
       <c r="F12">
-        <v>-4.213660074089775</v>
+        <v>-4.927955785718598</v>
       </c>
       <c r="G12">
-        <v>-1.852079231522521</v>
+        <v>-3.282364015763705</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>0.01773125190265516</v>
       </c>
       <c r="E13">
-        <v>-15.17101040334235</v>
+        <v>-16.46945522708766</v>
       </c>
       <c r="F13">
-        <v>-4.244905799948437</v>
+        <v>-4.397768262318484</v>
       </c>
       <c r="G13">
-        <v>-1.417295354213418</v>
+        <v>-3.466820992120817</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>0.4699831657843315</v>
       </c>
       <c r="E14">
-        <v>-15.19479847730464</v>
+        <v>-16.57613701776036</v>
       </c>
       <c r="F14">
-        <v>-4.06426276026271</v>
+        <v>-4.219658360244502</v>
       </c>
       <c r="G14">
-        <v>-0.04812655117271916</v>
+        <v>-2.456869553909817</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>0.8315336145186717</v>
       </c>
       <c r="E15">
-        <v>-16.73005984928108</v>
+        <v>-17.32379260490075</v>
       </c>
       <c r="F15">
-        <v>-3.804350488391492</v>
+        <v>-4.292532587943448</v>
       </c>
       <c r="G15">
-        <v>-0.6398302870432763</v>
+        <v>-1.856270382175238</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>1.078074816321254</v>
       </c>
       <c r="E16">
-        <v>-16.74402566312073</v>
+        <v>-16.90772999849802</v>
       </c>
       <c r="F16">
-        <v>-3.515255267616471</v>
+        <v>-4.298673407630565</v>
       </c>
       <c r="G16">
-        <v>0.05018671970701728</v>
+        <v>-1.798852280342119</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>1.198201816159948</v>
       </c>
       <c r="E17">
-        <v>-19.01880495444577</v>
+        <v>-18.40018823415395</v>
       </c>
       <c r="F17">
-        <v>-3.362708754576555</v>
+        <v>-3.962235674072355</v>
       </c>
       <c r="G17">
-        <v>0.5937087757990215</v>
+        <v>-0.68373805253063</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>1.185626616321342</v>
       </c>
       <c r="E18">
-        <v>-19.73402308226921</v>
+        <v>-20.30171258387077</v>
       </c>
       <c r="F18">
-        <v>-3.259090835794141</v>
+        <v>-3.373879424251107</v>
       </c>
       <c r="G18">
-        <v>0.9140470938155194</v>
+        <v>-0.2226485803664783</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>1.041827459501433</v>
       </c>
       <c r="E19">
-        <v>-20.54701549239226</v>
+        <v>-20.82311655263992</v>
       </c>
       <c r="F19">
-        <v>-2.943347387432978</v>
+        <v>-3.382927136146013</v>
       </c>
       <c r="G19">
-        <v>1.899540221582384</v>
+        <v>-0.7881096217472326</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>0.7739837283211295</v>
       </c>
       <c r="E20">
-        <v>-20.59086470620853</v>
+        <v>-20.62387275325044</v>
       </c>
       <c r="F20">
-        <v>-2.542688003444825</v>
+        <v>-3.080254012704972</v>
       </c>
       <c r="G20">
-        <v>1.064570978395102</v>
+        <v>0.2927768757337313</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>0.3900038603628709</v>
       </c>
       <c r="E21">
-        <v>-21.21743342685782</v>
+        <v>-22.22555325349738</v>
       </c>
       <c r="F21">
-        <v>-2.209982272876349</v>
+        <v>-3.014965736340981</v>
       </c>
       <c r="G21">
-        <v>1.155217025805886</v>
+        <v>0.3860283224839221</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.09536780310817783</v>
       </c>
       <c r="E22">
-        <v>-23.29761966159925</v>
+        <v>-22.90619648227226</v>
       </c>
       <c r="F22">
-        <v>-1.952246804785902</v>
+        <v>-2.453766083704731</v>
       </c>
       <c r="G22">
-        <v>1.539587915642967</v>
+        <v>0.5605139356767493</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.6720677370117466</v>
       </c>
       <c r="E23">
-        <v>-23.34267797797557</v>
+        <v>-23.05206768700733</v>
       </c>
       <c r="F23">
-        <v>-1.665592866679531</v>
+        <v>-2.493373776796914</v>
       </c>
       <c r="G23">
-        <v>0.80711647289706</v>
+        <v>-0.6755047257744625</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.321136096801917</v>
       </c>
       <c r="E24">
-        <v>-23.77269734126994</v>
+        <v>-23.33180964035716</v>
       </c>
       <c r="F24">
-        <v>-1.956589326406037</v>
+        <v>-2.092263828475819</v>
       </c>
       <c r="G24">
-        <v>1.409771493411526</v>
+        <v>-0.2206258370419836</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.031967822780201</v>
       </c>
       <c r="E25">
-        <v>-23.41631096534029</v>
+        <v>-24.57589013364039</v>
       </c>
       <c r="F25">
-        <v>-1.690632049055587</v>
+        <v>-2.180466745730304</v>
       </c>
       <c r="G25">
-        <v>1.248521441284705</v>
+        <v>-0.4631001239748232</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-2.781876381185346</v>
       </c>
       <c r="E26">
-        <v>-23.39363236750988</v>
+        <v>-23.25253870285289</v>
       </c>
       <c r="F26">
-        <v>-1.782438689120654</v>
+        <v>-2.191736397024571</v>
       </c>
       <c r="G26">
-        <v>0.3377837423401231</v>
+        <v>-0.4787457621934188</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.559229797201983</v>
       </c>
       <c r="E27">
-        <v>-24.07921163295312</v>
+        <v>-24.10769120598735</v>
       </c>
       <c r="F27">
-        <v>-1.657017891000384</v>
+        <v>-1.67783412155292</v>
       </c>
       <c r="G27">
-        <v>0.4240102114559804</v>
+        <v>-0.7067331018464077</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.338794703367142</v>
       </c>
       <c r="E28">
-        <v>-23.38906766571015</v>
+        <v>-23.91316607651387</v>
       </c>
       <c r="F28">
-        <v>-1.451109198992694</v>
+        <v>-2.249874241180353</v>
       </c>
       <c r="G28">
-        <v>0.04102975074539318</v>
+        <v>-1.096761714010103</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.103849210034369</v>
       </c>
       <c r="E29">
-        <v>-23.22789474730315</v>
+        <v>-24.9518485742312</v>
       </c>
       <c r="F29">
-        <v>-1.229495687274548</v>
+        <v>-2.057907704199233</v>
       </c>
       <c r="G29">
-        <v>0.1540550860016508</v>
+        <v>-0.9650086226381885</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.822648725217656</v>
       </c>
       <c r="E30">
-        <v>-23.0854063126518</v>
+        <v>-24.48498554641042</v>
       </c>
       <c r="F30">
-        <v>-1.521665673084394</v>
+        <v>-2.055774452331137</v>
       </c>
       <c r="G30">
-        <v>-0.04826228353982928</v>
+        <v>-1.132866523661395</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.473039623318534</v>
       </c>
       <c r="E31">
-        <v>-22.89816296938265</v>
+        <v>-23.56838165099187</v>
       </c>
       <c r="F31">
-        <v>-1.64866067488461</v>
+        <v>-2.198172577864917</v>
       </c>
       <c r="G31">
-        <v>-0.1713682299631676</v>
+        <v>-0.9127880773017248</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.024576582291684</v>
       </c>
       <c r="E32">
-        <v>-22.33148784595881</v>
+        <v>-22.57203585677225</v>
       </c>
       <c r="F32">
-        <v>-1.600386151170185</v>
+        <v>-2.082592928303188</v>
       </c>
       <c r="G32">
-        <v>-0.4031362126220042</v>
+        <v>-1.081255118704157</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.45948436096266</v>
       </c>
       <c r="E33">
-        <v>-21.73994234328485</v>
+        <v>-22.95400358237123</v>
       </c>
       <c r="F33">
-        <v>-1.662495137908932</v>
+        <v>-2.180594234056497</v>
       </c>
       <c r="G33">
-        <v>-0.4587533776817601</v>
+        <v>-0.8951196957586346</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.758491829385337</v>
       </c>
       <c r="E34">
-        <v>-22.0890107052181</v>
+        <v>-23.44724044281268</v>
       </c>
       <c r="F34">
-        <v>-1.636605505456285</v>
+        <v>-2.864260281427763</v>
       </c>
       <c r="G34">
-        <v>0.4887015818388787</v>
+        <v>-1.427180643193682</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.917528278353142</v>
       </c>
       <c r="E35">
-        <v>-21.78561653212621</v>
+        <v>-21.99315196742374</v>
       </c>
       <c r="F35">
-        <v>-1.79752507167113</v>
+        <v>-2.378681794400789</v>
       </c>
       <c r="G35">
-        <v>-0.03067997618076001</v>
+        <v>-0.7318733846716331</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.933619418437385</v>
       </c>
       <c r="E36">
-        <v>-20.47620374433432</v>
+        <v>-21.51251332167163</v>
       </c>
       <c r="F36">
-        <v>-1.559153575808761</v>
+        <v>-2.225288790549071</v>
       </c>
       <c r="G36">
-        <v>-0.3559179015953792</v>
+        <v>-0.705931949825904</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.818497160561059</v>
       </c>
       <c r="E37">
-        <v>-20.47916536633534</v>
+        <v>-21.61762373186366</v>
       </c>
       <c r="F37">
-        <v>-2.10101459551158</v>
+        <v>-2.220224890884453</v>
       </c>
       <c r="G37">
-        <v>0.2741385043476345</v>
+        <v>-1.062524052042961</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.58236137182008</v>
       </c>
       <c r="E38">
-        <v>-19.76125279647733</v>
+        <v>-21.11148977744837</v>
       </c>
       <c r="F38">
-        <v>-1.778088248970941</v>
+        <v>-2.454333842275416</v>
       </c>
       <c r="G38">
-        <v>0.664286296150744</v>
+        <v>-1.825243949381189</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.247538050668743</v>
       </c>
       <c r="E39">
-        <v>-20.43353193376004</v>
+        <v>-20.36836266431566</v>
       </c>
       <c r="F39">
-        <v>-1.932737923466561</v>
+        <v>-2.602096771597748</v>
       </c>
       <c r="G39">
-        <v>0.3384524725390559</v>
+        <v>-0.6516489346184744</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.830737727944429</v>
       </c>
       <c r="E40">
-        <v>-19.06681583587509</v>
+        <v>-19.59677409204474</v>
       </c>
       <c r="F40">
-        <v>-1.647165656500436</v>
+        <v>-2.265458699241235</v>
       </c>
       <c r="G40">
-        <v>0.2991231915325142</v>
+        <v>-0.7639525709471708</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.36065979902583</v>
       </c>
       <c r="E41">
-        <v>-19.11421990178738</v>
+        <v>-19.56151086494701</v>
       </c>
       <c r="F41">
-        <v>-1.627448517853214</v>
+        <v>-2.340109053124346</v>
       </c>
       <c r="G41">
-        <v>0.1451364763188542</v>
+        <v>-0.6538239630377756</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.856966949805524</v>
       </c>
       <c r="E42">
-        <v>-18.55819574922959</v>
+        <v>-18.67773387761006</v>
       </c>
       <c r="F42">
-        <v>-1.635905507441661</v>
+        <v>-2.339158037722125</v>
       </c>
       <c r="G42">
-        <v>0.4860531454074618</v>
+        <v>-1.080857853239445</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.350669683549008</v>
       </c>
       <c r="E43">
-        <v>-18.34980896081862</v>
+        <v>-18.66009547135019</v>
       </c>
       <c r="F43">
-        <v>-1.818979535707588</v>
+        <v>-2.432171461694757</v>
       </c>
       <c r="G43">
-        <v>0.7481059986595511</v>
+        <v>-1.335985045223379</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.859021839547037</v>
       </c>
       <c r="E44">
-        <v>-18.13960172585657</v>
+        <v>-17.19274762406678</v>
       </c>
       <c r="F44">
-        <v>-2.097081461870586</v>
+        <v>-2.152019428224222</v>
       </c>
       <c r="G44">
-        <v>1.170270076372952</v>
+        <v>-0.6969934768698718</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.408710583950121</v>
       </c>
       <c r="E45">
-        <v>-17.02598204026031</v>
+        <v>-17.3023321665784</v>
       </c>
       <c r="F45">
-        <v>-1.868339689827047</v>
+        <v>-2.349505180320648</v>
       </c>
       <c r="G45">
-        <v>0.7003315159823286</v>
+        <v>-0.8398567590715806</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.008802859922779</v>
       </c>
       <c r="E46">
-        <v>-16.19670523760568</v>
+        <v>-17.45271373142511</v>
       </c>
       <c r="F46">
-        <v>-2.153660939405575</v>
+        <v>-2.355422697473688</v>
       </c>
       <c r="G46">
-        <v>0.3547833936842806</v>
+        <v>-1.431202956023896</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.678118041589056</v>
       </c>
       <c r="E47">
-        <v>-15.90430619940441</v>
+        <v>-16.79165615273341</v>
       </c>
       <c r="F47">
-        <v>-2.388220455129481</v>
+        <v>-2.451904437401132</v>
       </c>
       <c r="G47">
-        <v>0.3641886535613501</v>
+        <v>-1.044352467577901</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.418681583379544</v>
       </c>
       <c r="E48">
-        <v>-15.90193327902439</v>
+        <v>-17.08090790149935</v>
       </c>
       <c r="F48">
-        <v>-2.160715557405901</v>
+        <v>-2.189935723398716</v>
       </c>
       <c r="G48">
-        <v>0.6704372897627098</v>
+        <v>-0.2701218033996272</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.239450520837105</v>
       </c>
       <c r="E49">
-        <v>-15.51892400440365</v>
+        <v>-15.50566463250919</v>
       </c>
       <c r="F49">
-        <v>-2.027463333533783</v>
+        <v>-2.541713232453872</v>
       </c>
       <c r="G49">
-        <v>0.1197710763969584</v>
+        <v>-1.88410875961497</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.134615062323174</v>
       </c>
       <c r="E50">
-        <v>-15.24794011978465</v>
+        <v>-15.10492185367441</v>
       </c>
       <c r="F50">
-        <v>-2.100649551298071</v>
+        <v>-2.16584122160122</v>
       </c>
       <c r="G50">
-        <v>0.422222516864774</v>
+        <v>-2.29196797005318</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.102134736368402</v>
       </c>
       <c r="E51">
-        <v>-14.44743724097476</v>
+        <v>-15.06070583346352</v>
       </c>
       <c r="F51">
-        <v>-2.060147064363665</v>
+        <v>-2.666422154765152</v>
       </c>
       <c r="G51">
-        <v>-0.05914404672741367</v>
+        <v>-1.590436885917301</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.131274360931569</v>
       </c>
       <c r="E52">
-        <v>-14.28340232699491</v>
+        <v>-13.58158848223418</v>
       </c>
       <c r="F52">
-        <v>-2.003299148676008</v>
+        <v>-2.483228556702609</v>
       </c>
       <c r="G52">
-        <v>0.3825787340320015</v>
+        <v>-1.616785517864361</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.212709479874606</v>
       </c>
       <c r="E53">
-        <v>-13.98440530216447</v>
+        <v>-14.32406802358379</v>
       </c>
       <c r="F53">
-        <v>-2.388543531136231</v>
+        <v>-2.359830942889314</v>
       </c>
       <c r="G53">
-        <v>0.1186885280056167</v>
+        <v>-1.74774738885239</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.331580895078993</v>
       </c>
       <c r="E54">
-        <v>-13.08466091547648</v>
+        <v>-14.15551369254429</v>
       </c>
       <c r="F54">
-        <v>-2.34608754295513</v>
+        <v>-2.354223040242743</v>
       </c>
       <c r="G54">
-        <v>-0.5033530471868215</v>
+        <v>-2.079404462067656</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.471533078619433</v>
       </c>
       <c r="E55">
-        <v>-12.97156680560892</v>
+        <v>-13.28863244172997</v>
       </c>
       <c r="F55">
-        <v>-2.114408788291409</v>
+        <v>-2.991715349796414</v>
       </c>
       <c r="G55">
-        <v>-0.2068638992352333</v>
+        <v>-1.018397790550015</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.616713443493857</v>
       </c>
       <c r="E56">
-        <v>-12.83612920498751</v>
+        <v>-12.29894350430163</v>
       </c>
       <c r="F56">
-        <v>-2.593835369689858</v>
+        <v>-2.852551943594919</v>
       </c>
       <c r="G56">
-        <v>-0.1458075078544548</v>
+        <v>-1.825522035206488</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.750620101670833</v>
       </c>
       <c r="E57">
-        <v>-12.92696586510737</v>
+        <v>-12.81240000118732</v>
       </c>
       <c r="F57">
-        <v>-2.261332353478557</v>
+        <v>-2.363132177870047</v>
       </c>
       <c r="G57">
-        <v>-0.9464993625281234</v>
+        <v>-1.447080332430241</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.862774676637887</v>
       </c>
       <c r="E58">
-        <v>-11.93483155171489</v>
+        <v>-11.93315601633205</v>
       </c>
       <c r="F58">
-        <v>-2.465324761328566</v>
+        <v>-2.714601656124651</v>
       </c>
       <c r="G58">
-        <v>-1.208628358327616</v>
+        <v>-3.151461734595383</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.941933001833955</v>
       </c>
       <c r="E59">
-        <v>-11.97478174941056</v>
+        <v>-11.83481114630747</v>
       </c>
       <c r="F59">
-        <v>-2.65788360432206</v>
+        <v>-2.4689799545814</v>
       </c>
       <c r="G59">
-        <v>-0.7895199141469622</v>
+        <v>-2.232748931446697</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.986359097252906</v>
       </c>
       <c r="E60">
-        <v>-12.12912572901399</v>
+        <v>-11.68264989117574</v>
       </c>
       <c r="F60">
-        <v>-2.705288673488909</v>
+        <v>-2.893888251693804</v>
       </c>
       <c r="G60">
-        <v>-1.753431595543318</v>
+        <v>-3.354331965241922</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.993005747184305</v>
       </c>
       <c r="E61">
-        <v>-12.05725884651226</v>
+        <v>-11.41210526853549</v>
       </c>
       <c r="F61">
-        <v>-2.797734338890856</v>
+        <v>-2.820063800445594</v>
       </c>
       <c r="G61">
-        <v>-1.155394786056135</v>
+        <v>-3.383355517984712</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.969892465818679</v>
       </c>
       <c r="E62">
-        <v>-11.24389510152058</v>
+        <v>-11.18606648844263</v>
       </c>
       <c r="F62">
-        <v>-2.747800883230008</v>
+        <v>-3.015257930082379</v>
       </c>
       <c r="G62">
-        <v>-1.682125755172956</v>
+        <v>-3.071684208190026</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.921838259536447</v>
       </c>
       <c r="E63">
-        <v>-11.64526733824242</v>
+        <v>-10.08970934576361</v>
       </c>
       <c r="F63">
-        <v>-2.916594635256417</v>
+        <v>-2.850046520836694</v>
       </c>
       <c r="G63">
-        <v>-1.836261444935883</v>
+        <v>-2.918303322810053</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.861839511869513</v>
       </c>
       <c r="E64">
-        <v>-11.21924208902282</v>
+        <v>-11.38065048807822</v>
       </c>
       <c r="F64">
-        <v>-3.189672254402683</v>
+        <v>-2.82697588491353</v>
       </c>
       <c r="G64">
-        <v>-1.682615715912768</v>
+        <v>-3.447421195260688</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.795413468818162</v>
       </c>
       <c r="E65">
-        <v>-10.97623058834921</v>
+        <v>-11.01055642132735</v>
       </c>
       <c r="F65">
-        <v>-2.773268458056189</v>
+        <v>-3.079687045987245</v>
       </c>
       <c r="G65">
-        <v>-1.914923317494506</v>
+        <v>-3.82056933571964</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-3.733912313081524</v>
       </c>
       <c r="E66">
-        <v>-11.21098215243283</v>
+        <v>-11.14994285128344</v>
       </c>
       <c r="F66">
-        <v>-3.220377144691223</v>
+        <v>-3.263404850707798</v>
       </c>
       <c r="G66">
-        <v>-2.155573493835207</v>
+        <v>-4.285873132355284</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.679345667234993</v>
       </c>
       <c r="E67">
-        <v>-11.29021686214504</v>
+        <v>-10.93100924690861</v>
       </c>
       <c r="F67">
-        <v>-2.673886160744618</v>
+        <v>-3.116668162818671</v>
       </c>
       <c r="G67">
-        <v>-2.197703496367972</v>
+        <v>-4.771708932425487</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.638864701820127</v>
       </c>
       <c r="E68">
-        <v>-10.86246626432851</v>
+        <v>-10.24907540304155</v>
       </c>
       <c r="F68">
-        <v>-2.994787739272367</v>
+        <v>-3.304730072865275</v>
       </c>
       <c r="G68">
-        <v>-2.378839995549195</v>
+        <v>-4.560764281208667</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.609282144589433</v>
       </c>
       <c r="E69">
-        <v>-10.70237565120935</v>
+        <v>-10.36802482980102</v>
       </c>
       <c r="F69">
-        <v>-2.950246010400632</v>
+        <v>-3.672393735958204</v>
       </c>
       <c r="G69">
-        <v>-2.270787099692923</v>
+        <v>-5.056919051724779</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.592591824148721</v>
       </c>
       <c r="E70">
-        <v>-11.64399483704627</v>
+        <v>-11.22841224888835</v>
       </c>
       <c r="F70">
-        <v>-3.131216085357898</v>
+        <v>-3.437914989235986</v>
       </c>
       <c r="G70">
-        <v>-2.678384777033531</v>
+        <v>-4.243905346553943</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.580995739531905</v>
       </c>
       <c r="E71">
-        <v>-10.57093669313672</v>
+        <v>-9.826985397734607</v>
       </c>
       <c r="F71">
-        <v>-3.404282618562756</v>
+        <v>-3.627440243548456</v>
       </c>
       <c r="G71">
-        <v>-2.589804510039252</v>
+        <v>-4.521431689656586</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.572718248802055</v>
       </c>
       <c r="E72">
-        <v>-12.19474331738513</v>
+        <v>-10.22231665013022</v>
       </c>
       <c r="F72">
-        <v>-3.280010799084138</v>
+        <v>-3.253434630117149</v>
       </c>
       <c r="G72">
-        <v>-2.853277587327688</v>
+        <v>-4.057210441412284</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.557433903052694</v>
       </c>
       <c r="E73">
-        <v>-10.9279932832195</v>
+        <v>-9.732666341102849</v>
       </c>
       <c r="F73">
-        <v>-3.610144591245941</v>
+        <v>-3.530665518026655</v>
       </c>
       <c r="G73">
-        <v>-3.079099830197994</v>
+        <v>-4.742314598582299</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.53282698756389</v>
       </c>
       <c r="E74">
-        <v>-12.10848041601302</v>
+        <v>-10.86569053782197</v>
       </c>
       <c r="F74">
-        <v>-3.457763575474189</v>
+        <v>-3.620940714471492</v>
       </c>
       <c r="G74">
-        <v>-3.005698414501273</v>
+        <v>-4.278447578710699</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.490570621798148</v>
       </c>
       <c r="E75">
-        <v>-11.52368686808449</v>
+        <v>-11.22420076806122</v>
       </c>
       <c r="F75">
-        <v>-3.344739235407022</v>
+        <v>-3.561060001955769</v>
       </c>
       <c r="G75">
-        <v>-2.294967324311759</v>
+        <v>-3.978551879399201</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.432016993827487</v>
       </c>
       <c r="E76">
-        <v>-12.28060318457056</v>
+        <v>-12.28489617792983</v>
       </c>
       <c r="F76">
-        <v>-3.67928127298445</v>
+        <v>-3.510593629254375</v>
       </c>
       <c r="G76">
-        <v>-2.689498278408864</v>
+        <v>-4.522083867127822</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.354006486426261</v>
       </c>
       <c r="E77">
-        <v>-12.73452383367741</v>
+        <v>-12.29797893933799</v>
       </c>
       <c r="F77">
-        <v>-3.570654884244459</v>
+        <v>-3.475558095140066</v>
       </c>
       <c r="G77">
-        <v>-2.944605607119562</v>
+        <v>-4.079963820903695</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.263729681541706</v>
       </c>
       <c r="E78">
-        <v>-13.20974642451635</v>
+        <v>-12.50425998733539</v>
       </c>
       <c r="F78">
-        <v>-3.433745883413592</v>
+        <v>-3.865843413529133</v>
       </c>
       <c r="G78">
-        <v>-2.250195506438656</v>
+        <v>-3.878133101556487</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.164539612866405</v>
       </c>
       <c r="E79">
-        <v>-13.51090805992246</v>
+        <v>-12.46353542058441</v>
       </c>
       <c r="F79">
-        <v>-3.620644561465305</v>
+        <v>-3.487416093181919</v>
       </c>
       <c r="G79">
-        <v>-2.691792486467579</v>
+        <v>-3.892626669927417</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.068203279279763</v>
       </c>
       <c r="E80">
-        <v>-14.60744181308777</v>
+        <v>-13.25699652231238</v>
       </c>
       <c r="F80">
-        <v>-3.408795388568801</v>
+        <v>-3.648153533216488</v>
       </c>
       <c r="G80">
-        <v>-2.930939675133451</v>
+        <v>-4.114578885062314</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.980641859442063</v>
       </c>
       <c r="E81">
-        <v>-14.89961895606267</v>
+        <v>-14.34556921817221</v>
       </c>
       <c r="F81">
-        <v>-3.653644241625317</v>
+        <v>-3.80010774024403</v>
       </c>
       <c r="G81">
-        <v>-2.402745444888272</v>
+        <v>-3.203510131563805</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.913031859557733</v>
       </c>
       <c r="E82">
-        <v>-16.13428022340994</v>
+        <v>-15.29415772550694</v>
       </c>
       <c r="F82">
-        <v>-3.611348207741675</v>
+        <v>-3.758886250824014</v>
       </c>
       <c r="G82">
-        <v>-1.968286001042018</v>
+        <v>-3.430881709746489</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.87077901856775</v>
       </c>
       <c r="E83">
-        <v>-16.80441286401302</v>
+        <v>-15.74832291221021</v>
       </c>
       <c r="F83">
-        <v>-3.461136869074075</v>
+        <v>-3.746768525012029</v>
       </c>
       <c r="G83">
-        <v>-3.093993974579175</v>
+        <v>-4.08166213076534</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.861461308816553</v>
       </c>
       <c r="E84">
-        <v>-18.12474833111141</v>
+        <v>-16.12749204087244</v>
       </c>
       <c r="F84">
-        <v>-3.190277230062381</v>
+        <v>-3.919470071384786</v>
       </c>
       <c r="G84">
-        <v>-1.960903484489444</v>
+        <v>-3.212895528167639</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.888097972520911</v>
       </c>
       <c r="E85">
-        <v>-18.37815267963263</v>
+        <v>-18.4074202071442</v>
       </c>
       <c r="F85">
-        <v>-3.795499947883059</v>
+        <v>-3.562400609013188</v>
       </c>
       <c r="G85">
-        <v>-2.096672267600494</v>
+        <v>-2.839456059701231</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.952882082383173</v>
       </c>
       <c r="E86">
-        <v>-20.61955258904712</v>
+        <v>-18.93347491871923</v>
       </c>
       <c r="F86">
-        <v>-3.239922451246619</v>
+        <v>-3.896091404661068</v>
       </c>
       <c r="G86">
-        <v>-1.757050021817742</v>
+        <v>-3.08529386090197</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.055394748085619</v>
       </c>
       <c r="E87">
-        <v>-20.55749438124601</v>
+        <v>-20.75611777969644</v>
       </c>
       <c r="F87">
-        <v>-3.526068811607092</v>
+        <v>-3.957904238393628</v>
       </c>
       <c r="G87">
-        <v>-1.978492412939591</v>
+        <v>-3.049487000349213</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.191768758648141</v>
       </c>
       <c r="E88">
-        <v>-23.6084858168038</v>
+        <v>-21.51436093906676</v>
       </c>
       <c r="F88">
-        <v>-3.59408422955747</v>
+        <v>-3.457798417004328</v>
       </c>
       <c r="G88">
-        <v>-1.552815846409023</v>
+        <v>-3.060285999898316</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.358645315801763</v>
       </c>
       <c r="E89">
-        <v>-25.1013380296984</v>
+        <v>-24.27525380121918</v>
       </c>
       <c r="F89">
-        <v>-3.547315810168628</v>
+        <v>-3.688825476683846</v>
       </c>
       <c r="G89">
-        <v>-1.445050968014668</v>
+        <v>-3.677752401155481</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.548160977797696</v>
       </c>
       <c r="E90">
-        <v>-25.81681880901429</v>
+        <v>-23.94110223266719</v>
       </c>
       <c r="F90">
-        <v>-3.159436141065113</v>
+        <v>-3.628034925119703</v>
       </c>
       <c r="G90">
-        <v>-1.681864222075354</v>
+        <v>-2.415302344118728</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.757486983732713</v>
       </c>
       <c r="E91">
-        <v>-29.33043462072167</v>
+        <v>-28.80080694315458</v>
       </c>
       <c r="F91">
-        <v>-3.309309358519768</v>
+        <v>-3.200728897251324</v>
       </c>
       <c r="G91">
-        <v>-1.993823549331956</v>
+        <v>-2.902637821318222</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.978407166958475</v>
       </c>
       <c r="E92">
-        <v>-29.90190086964562</v>
+        <v>-29.83668405122416</v>
       </c>
       <c r="F92">
-        <v>-3.22374331161449</v>
+        <v>-3.434636717991026</v>
       </c>
       <c r="G92">
-        <v>-1.635622521982814</v>
+        <v>-2.773847668203955</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.21137656779096</v>
       </c>
       <c r="E93">
-        <v>-33.35367131183025</v>
+        <v>-31.62520259631656</v>
       </c>
       <c r="F93">
-        <v>-3.208847765626824</v>
+        <v>-3.70077691337471</v>
       </c>
       <c r="G93">
-        <v>-1.601126637463608</v>
+        <v>-2.984401675047141</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.448364564519294</v>
       </c>
       <c r="E94">
-        <v>-34.80918625653162</v>
+        <v>-33.80110265768412</v>
       </c>
       <c r="F94">
-        <v>-3.386947373612356</v>
+        <v>-3.426844093034107</v>
       </c>
       <c r="G94">
-        <v>-2.608068789779411</v>
+        <v>-2.593207750853622</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.690791250780733</v>
       </c>
       <c r="E95">
-        <v>-37.1298050259993</v>
+        <v>-37.08414442257995</v>
       </c>
       <c r="F95">
-        <v>-3.392699393497232</v>
+        <v>-3.556227323354805</v>
       </c>
       <c r="G95">
-        <v>-2.750865861070334</v>
+        <v>-3.457515048609926</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.927072361354429</v>
       </c>
       <c r="E96">
-        <v>-39.95449502997177</v>
+        <v>-37.81844553987172</v>
       </c>
       <c r="F96">
-        <v>-2.959315102325396</v>
+        <v>-3.203574816781368</v>
       </c>
       <c r="G96">
-        <v>-2.298003094571271</v>
+        <v>-3.097857381223504</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.155318414140281</v>
       </c>
       <c r="E97">
-        <v>-41.90959801991033</v>
+        <v>-40.69736175584904</v>
       </c>
       <c r="F97">
-        <v>-3.220218774099679</v>
+        <v>-4.024571130757009</v>
       </c>
       <c r="G97">
-        <v>-2.95688110997918</v>
+        <v>-4.711897306167475</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.358775902634559</v>
       </c>
       <c r="E98">
-        <v>-44.38231238163664</v>
+        <v>-42.88352107508097</v>
       </c>
       <c r="F98">
-        <v>-3.06065881941324</v>
+        <v>-3.549677907541505</v>
       </c>
       <c r="G98">
-        <v>-2.790820835183798</v>
+        <v>-3.858034779587572</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.5350507503277</v>
       </c>
       <c r="E99">
-        <v>-46.97212628849028</v>
+        <v>-46.64655617818283</v>
       </c>
       <c r="F99">
-        <v>-3.275524952078656</v>
+        <v>-3.905745675921587</v>
       </c>
       <c r="G99">
-        <v>-3.33639874005569</v>
+        <v>-4.068943014803461</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.6633078274093</v>
       </c>
       <c r="E100">
-        <v>-49.43790755651084</v>
+        <v>-48.10086202032414</v>
       </c>
       <c r="F100">
-        <v>-3.431961838699849</v>
+        <v>-3.559133423709637</v>
       </c>
       <c r="G100">
-        <v>-4.151680168920926</v>
+        <v>-5.242802873209317</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.743178720149627</v>
       </c>
       <c r="E101">
-        <v>-51.48783679217001</v>
+        <v>-50.33621302058289</v>
       </c>
       <c r="F101">
-        <v>-3.076544181598055</v>
+        <v>-3.644940193914061</v>
       </c>
       <c r="G101">
-        <v>-4.592426338746256</v>
+        <v>-4.801927592107955</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.745374420876209</v>
       </c>
       <c r="E102">
-        <v>-53.23077285001971</v>
+        <v>-51.60726736929281</v>
       </c>
       <c r="F102">
-        <v>-3.337219799720515</v>
+        <v>-3.212895717946687</v>
       </c>
       <c r="G102">
-        <v>-4.439091801003833</v>
+        <v>-5.014040865900139</v>
       </c>
     </row>
   </sheetData>
